--- a/DATA/DISENO_EXPERIMENTAL/variables_objetivo.xlsx
+++ b/DATA/DISENO_EXPERIMENTAL/variables_objetivo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,22 +446,42 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Variable_Objetivo_Modelo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Tipo_Problema</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Existe_Dataset</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Registros_Disponibles</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Cobertura_%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Existe_Objetivo_Modelo</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Registros_Objetivo_Modelo</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Cobertura_Objetivo_Modelo_%</t>
         </is>
       </c>
     </row>
@@ -481,16 +501,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>nivel_de_riesgo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Clasificación</t>
         </is>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
         <v>528</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>528</v>
+      </c>
+      <c r="K2" t="n">
         <v>100</v>
       </c>
     </row>
@@ -510,16 +544,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>CALIDAD DEL AGUA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Clasificación</t>
         </is>
       </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
         <v>96</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>96</v>
+      </c>
+      <c r="K3" t="n">
         <v>18.18</v>
       </c>
     </row>
@@ -539,16 +587,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Nivel_Minimo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
         <v>87</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>87</v>
+      </c>
+      <c r="K4" t="n">
         <v>16.48</v>
       </c>
     </row>
@@ -568,16 +630,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>VolumenUtilDiarioMasa</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
         <v>336</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>336</v>
+      </c>
+      <c r="K5" t="n">
         <v>63.64</v>
       </c>
     </row>
@@ -597,16 +673,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
         <v>26</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>26</v>
+      </c>
+      <c r="K6" t="n">
         <v>4.92</v>
       </c>
     </row>
@@ -626,16 +716,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
         <v>49</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>49</v>
+      </c>
+      <c r="K7" t="n">
         <v>9.279999999999999</v>
       </c>
     </row>
@@ -655,16 +759,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
         <v>50</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>50</v>
+      </c>
+      <c r="K8" t="n">
         <v>9.470000000000001</v>
       </c>
     </row>
@@ -684,16 +802,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Regresión</t>
         </is>
       </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
         <v>50</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>50</v>
+      </c>
+      <c r="K9" t="n">
         <v>9.470000000000001</v>
       </c>
     </row>
